--- a/Overture-Match-Suggestions/ZW.xlsx
+++ b/Overture-Match-Suggestions/ZW.xlsx
@@ -644,10 +644,24 @@
           <t>BulawayoZimbabwe</t>
         </is>
       </c>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
-      <c r="P2" s="2" t="n"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>ZW-BU</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Bulawayo</t>
+        </is>
+      </c>
       <c r="Q2" s="2" t="n"/>
       <c r="R2" s="2" t="n"/>
       <c r="S2" s="2" t="n"/>
@@ -748,10 +762,24 @@
           <t>HarareZimbabwe</t>
         </is>
       </c>
-      <c r="M3" s="3" t="n"/>
-      <c r="N3" s="3" t="n"/>
-      <c r="O3" s="3" t="n"/>
-      <c r="P3" s="3" t="n"/>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>ZW-HA</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>Harare Province</t>
+        </is>
+      </c>
       <c r="Q3" s="3" t="n"/>
       <c r="R3" s="3" t="n"/>
       <c r="S3" s="3" t="n"/>
@@ -838,10 +866,24 @@
           <t>HarareZimbabwe</t>
         </is>
       </c>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
-      <c r="O4" s="3" t="n"/>
-      <c r="P4" s="3" t="n"/>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>ZW-HA</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Harare Province</t>
+        </is>
+      </c>
       <c r="Q4" s="3" t="n"/>
       <c r="R4" s="3" t="n"/>
       <c r="S4" s="3" t="n"/>
@@ -928,10 +970,24 @@
           <t>HarareZimbabwe</t>
         </is>
       </c>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="n"/>
-      <c r="P5" s="3" t="n"/>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>ZW-HA</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Harare Province</t>
+        </is>
+      </c>
       <c r="Q5" s="3" t="n"/>
       <c r="R5" s="3" t="n"/>
       <c r="S5" s="3" t="n"/>
@@ -1018,10 +1074,24 @@
           <t>HarareZimbabwe</t>
         </is>
       </c>
-      <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>ZW-HA</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Harare Province</t>
+        </is>
+      </c>
       <c r="Q6" s="2" t="n"/>
       <c r="R6" s="2" t="n"/>
       <c r="S6" s="2" t="n"/>
@@ -1120,10 +1190,24 @@
           <t>ManicalandZimbabwe</t>
         </is>
       </c>
-      <c r="M7" s="3" t="n"/>
-      <c r="N7" s="3" t="n"/>
-      <c r="O7" s="3" t="n"/>
-      <c r="P7" s="3" t="n"/>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>ZW-MA</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Mutare</t>
+        </is>
+      </c>
       <c r="Q7" s="3" t="n"/>
       <c r="R7" s="3" t="n"/>
       <c r="S7" s="3" t="n"/>
@@ -1210,10 +1294,24 @@
           <t>ManicalandZimbabwe</t>
         </is>
       </c>
-      <c r="M8" s="3" t="n"/>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
-      <c r="P8" s="3" t="n"/>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>ZW-MA</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>Mutare</t>
+        </is>
+      </c>
       <c r="Q8" s="3" t="n"/>
       <c r="R8" s="3" t="n"/>
       <c r="S8" s="3" t="n"/>
@@ -2966,10 +3064,24 @@
           <t>Mashonaland EastZimbabwe</t>
         </is>
       </c>
-      <c r="M27" s="2" t="n"/>
-      <c r="N27" s="2" t="n"/>
-      <c r="O27" s="2" t="n"/>
-      <c r="P27" s="2" t="n"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>ZW-ME</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>Goromonzi</t>
+        </is>
+      </c>
       <c r="Q27" s="2" t="n"/>
       <c r="R27" s="2" t="n"/>
       <c r="S27" s="2" t="n"/>
@@ -3546,10 +3658,24 @@
           <t>Mashonaland EastZimbabwe</t>
         </is>
       </c>
-      <c r="M33" s="3" t="n"/>
-      <c r="N33" s="3" t="n"/>
-      <c r="O33" s="3" t="n"/>
-      <c r="P33" s="3" t="n"/>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>ZW-ME</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>Marondera</t>
+        </is>
+      </c>
       <c r="Q33" s="3" t="n"/>
       <c r="R33" s="3" t="n"/>
       <c r="S33" s="3" t="n"/>
@@ -3924,10 +4050,24 @@
           <t>Mashonaland EastZimbabwe</t>
         </is>
       </c>
-      <c r="M37" s="3" t="n"/>
-      <c r="N37" s="3" t="n"/>
-      <c r="O37" s="3" t="n"/>
-      <c r="P37" s="3" t="n"/>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>ZW-ME</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>Marondera</t>
+        </is>
+      </c>
       <c r="Q37" s="3" t="n"/>
       <c r="R37" s="3" t="n"/>
       <c r="S37" s="3" t="n"/>
@@ -5160,10 +5300,24 @@
           <t>MasvingoZimbabwe</t>
         </is>
       </c>
-      <c r="M51" s="3" t="n"/>
-      <c r="N51" s="3" t="n"/>
-      <c r="O51" s="3" t="n"/>
-      <c r="P51" s="3" t="n"/>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>ZW-MV</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>Masvingo</t>
+        </is>
+      </c>
       <c r="Q51" s="3" t="n"/>
       <c r="R51" s="3" t="n"/>
       <c r="S51" s="3" t="n"/>
@@ -5992,10 +6146,24 @@
           <t>Matabeleland NorthZimbabwe</t>
         </is>
       </c>
-      <c r="M60" s="2" t="n"/>
-      <c r="N60" s="2" t="n"/>
-      <c r="O60" s="2" t="n"/>
-      <c r="P60" s="2" t="n"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>ZW-MN</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>Umguza</t>
+        </is>
+      </c>
       <c r="Q60" s="2" t="n"/>
       <c r="R60" s="2" t="n"/>
       <c r="S60" s="2" t="n"/>
@@ -7734,10 +7902,24 @@
           <t>MidlandsZimbabwe</t>
         </is>
       </c>
-      <c r="M79" s="3" t="n"/>
-      <c r="N79" s="3" t="n"/>
-      <c r="O79" s="3" t="n"/>
-      <c r="P79" s="3" t="n"/>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O79" s="3" t="inlineStr">
+        <is>
+          <t>ZW-MI</t>
+        </is>
+      </c>
+      <c r="P79" s="3" t="inlineStr">
+        <is>
+          <t>Gweru</t>
+        </is>
+      </c>
       <c r="Q79" s="3" t="n"/>
       <c r="R79" s="3" t="n"/>
       <c r="S79" s="3" t="n"/>
@@ -7824,10 +8006,24 @@
           <t>MidlandsZimbabwe</t>
         </is>
       </c>
-      <c r="M80" s="3" t="n"/>
-      <c r="N80" s="3" t="n"/>
-      <c r="O80" s="3" t="n"/>
-      <c r="P80" s="3" t="n"/>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O80" s="3" t="inlineStr">
+        <is>
+          <t>ZW-MI</t>
+        </is>
+      </c>
+      <c r="P80" s="3" t="inlineStr">
+        <is>
+          <t>Gweru</t>
+        </is>
+      </c>
       <c r="Q80" s="3" t="n"/>
       <c r="R80" s="3" t="n"/>
       <c r="S80" s="3" t="n"/>
@@ -7914,10 +8110,24 @@
           <t>MidlandsZimbabwe</t>
         </is>
       </c>
-      <c r="M81" s="3" t="n"/>
-      <c r="N81" s="3" t="n"/>
-      <c r="O81" s="3" t="n"/>
-      <c r="P81" s="3" t="n"/>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O81" s="3" t="inlineStr">
+        <is>
+          <t>ZW-MI</t>
+        </is>
+      </c>
+      <c r="P81" s="3" t="inlineStr">
+        <is>
+          <t>Kwekwe</t>
+        </is>
+      </c>
       <c r="Q81" s="3" t="n"/>
       <c r="R81" s="3" t="n"/>
       <c r="S81" s="3" t="n"/>
